--- a/AAII_Financials/Quarterly/MKKGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MKKGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="92">
   <si>
     <t>MKKGY</t>
   </si>
@@ -656,125 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -817,44 +821,47 @@
       <c r="P8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R8" s="3">
         <v>6269000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6274500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6058500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5639800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5651400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5355400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5152500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4727300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4586000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4615500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4493500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4767300</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -897,44 +904,47 @@
       <c r="P9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R9" s="3">
         <v>2529800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2320300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2294800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2155900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2123800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2002000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1918200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1756800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1790300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1843300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1756400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1804400</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -977,44 +987,47 @@
       <c r="P10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R10" s="3">
         <v>3739300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3954300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3763700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3483900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3527700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3353500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3234300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2970500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2795700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2772200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2737100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2962900</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,44 +1101,47 @@
       <c r="P12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R12" s="3">
         <v>768700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>693800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>652900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>635800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>639600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>710800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>618900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>585900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>656300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>551100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>567300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>631600</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1247,44 +1267,47 @@
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-6500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-6500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>6100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1327,8 +1350,8 @@
       <c r="P15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,8 +1416,9 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1434,44 +1461,47 @@
       <c r="P17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R17" s="3">
         <v>5284400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4941000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4777800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4367100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4525000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4227900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4042600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3662600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3976600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3404300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3957800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3986200</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1514,44 +1544,47 @@
       <c r="P18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R18" s="3">
         <v>984700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1333600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1280700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1272700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1126400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1127500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1109800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1064700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>609400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1211200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>535600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>781100</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,8 +1613,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1624,44 +1658,47 @@
       <c r="P20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R20" s="3">
         <v>-55400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-50800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-59800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-36900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-51000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-58200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-99500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-60200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-51900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-105900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-111300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1704,33 +1741,33 @@
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3">
         <v>1591600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1790700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1799700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1702400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1590400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1547500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1453700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1437300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1740,8 +1777,11 @@
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1784,8 +1824,8 @@
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1820,8 +1860,11 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1864,44 +1907,47 @@
       <c r="P23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R23" s="3">
         <v>929300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1282800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1220800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1235800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1075400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1069400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1010400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1004500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>557500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1105400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>424400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>673100</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1944,44 +1990,47 @@
       <c r="P24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R24" s="3">
         <v>199400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>282100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>274200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>276700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>201600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>246600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>220100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>240900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>118700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>267800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>109100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>173500</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,8 +2109,11 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2104,44 +2156,47 @@
       <c r="P26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R26" s="3">
         <v>729900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1000700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>946600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>959100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>873800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>822800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>790300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>763600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>438900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>837600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>315300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>499600</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2184,44 +2239,47 @@
       <c r="P27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R27" s="3">
         <v>725500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>997500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>943400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>954800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>869400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>819500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>788200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>762500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>434900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>835500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>316400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>497500</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2344,8 +2405,8 @@
       <c r="P29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2362,14 +2423,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>16</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2377,11 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2607,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2584,44 +2654,47 @@
       <c r="P32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R32" s="3">
         <v>55400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>50800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>59800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>36900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>51000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>58200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>99500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>60200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>51900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>105900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>111300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2664,44 +2737,47 @@
       <c r="P33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R33" s="3">
         <v>725500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>997500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>943400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>954800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>869400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>819500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>788200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>762500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>434900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>835500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>316400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>497500</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,8 +2856,11 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2824,129 +2903,135 @@
       <c r="P35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R35" s="3">
         <v>725500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>997500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>943400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>954800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>869400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>819500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>788200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>762500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>434900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>835500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>316400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>497500</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,728 +3091,756 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2233500</v>
+      </c>
+      <c r="E41" s="3">
         <v>3162700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3217100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2641100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1369300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1086300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2605900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3525500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2876900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2395100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2190800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2503200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1922500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1721000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2053500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1733400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1719200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1452800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2058700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1640100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1930900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2284600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1351500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1606700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>852000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5575600</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1334400</v>
+      </c>
+      <c r="E42" s="3">
         <v>1189200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>701000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>789600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>478000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>664700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>578700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>779600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>139300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>284800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>476400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>230700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>181200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>148800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>355500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>375000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>144700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>115000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>188600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>152900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>47600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>61200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>124700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>88200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>62200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5603800</v>
+      </c>
+      <c r="E43" s="3">
         <v>5510000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5600600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5507500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5728700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5380500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5072000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4978800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5191300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5050200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5421700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5155600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5290400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5242300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5192400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5183000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5295800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5104900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4710400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4530500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4363200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4313900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3899800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4253300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4617800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4107300</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5582100</v>
+      </c>
+      <c r="E44" s="3">
         <v>5514000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5356300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5291600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5247200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4877900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4642300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4913000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5050900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5087900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5125500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5261400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5454100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5312900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5130400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5252200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4868200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4495200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4228000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4049100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3770700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3534000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3285400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3557900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3645800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3420000</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>976800</v>
+      </c>
+      <c r="E45" s="3">
         <v>952700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>445000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>877600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1499700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1406200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>851000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1338400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>721100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1016300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>283000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1207700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1364600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1646000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>782000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1443800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1482000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>859300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>719800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>735500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>660200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>644100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>594500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1140700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>643600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1344000</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15730600</v>
+      </c>
+      <c r="E46" s="3">
         <v>16328600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15533600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15107400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14323000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13415500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13924800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15535400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13979400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13834300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13698500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14358600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14212900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14071100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13513800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13987500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13509800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12027200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11905600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11108200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10772600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10837800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9255900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10646800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9821500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14746900</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1173300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1149700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>906400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1159200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1214300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1132700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>998000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1219000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1141100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1155500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>893100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1051000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1139700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1045200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1104300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1082900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1023900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1019900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1028800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>897100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>828400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>824800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>846800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>707800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>829100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>714500</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11488600</v>
+      </c>
+      <c r="E48" s="3">
         <v>11580800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11670800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11470100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11348200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10650700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10378900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10500800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10107100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9940700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10009900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9228400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9162700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8928700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9086800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8587200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8240200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7923800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7823900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7280900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6983900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6688300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6404300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6255400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6777800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5864700</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29720100</v>
+      </c>
+      <c r="E49" s="3">
         <v>30030800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>30050500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>30076300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26923100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26541300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26354700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>26698600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>26282000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26607000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26965800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26653300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27147400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>27195800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>28491900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>29842400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>28763900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>27461400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>26686200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>26166500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>25349700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24811600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23550600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>25619500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>28708400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>22951700</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>197600</v>
+      </c>
+      <c r="E52" s="3">
         <v>179400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>433300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>178300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>171500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>154600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>393400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>179600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>180000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>187700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>358100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>138700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>132100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>143400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1559500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1543200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1471100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1732700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1732400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1754300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1712900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1641400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1629800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1639900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1657100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1613500</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>60193100</v>
+      </c>
+      <c r="E54" s="3">
         <v>61189700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>60499000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>59752400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>55610100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>53364700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>53417500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>55924600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>53439400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>53408100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>53603400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52821800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>53255500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>52843300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>53757400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55043300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>53009000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>50165000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49176900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>47207000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>45647400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44803900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>41687300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>44869500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>47793900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>45891300</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,488 +4315,507 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2362600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2455000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1669600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2262100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2301800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2261100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1555000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2174900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2273700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2250500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1956400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2375100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2623400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2527200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2767900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2642300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2672400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2556300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2580200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2296000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2229200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1977300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1763400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1747800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2240700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1893800</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1249900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1425300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1453600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1937100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3644200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1874200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3420600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3912600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3136200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2299100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>775900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1498700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1845000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1613400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2653800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1895500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2610400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2522600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2743900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2983000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3468100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3416600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2350900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3822600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4963600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4287300</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5545500</v>
+      </c>
+      <c r="E59" s="3">
         <v>6812400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5565300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5847700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5552600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6073300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5027400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5503000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5152700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6085900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5284600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5187300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5073100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6098400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6441800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5633700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5291400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5995700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5985300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5267100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4692200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5479700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5092700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4506600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5714200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4351600</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9282500</v>
+      </c>
+      <c r="E60" s="3">
         <v>10779800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10616400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10133800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11578400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10270200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11693800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11669600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10640700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10722800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9615300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9192400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9657200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10382400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10537700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10171500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10574200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11074600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11309300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10546100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10389600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10873600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9207000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10077000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12918600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10532700</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12804800</v>
+      </c>
+      <c r="E61" s="3">
         <v>12455200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12598300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12264500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7397500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7527000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7244000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8793200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8381000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8440000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10212200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10097400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10365700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9951100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10189900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10013800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10211800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8990300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8965500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8825200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9226800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9188200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9759600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10355100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9429800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9397100</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>570100</v>
+      </c>
+      <c r="E62" s="3">
         <v>465600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>476700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>488100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>496800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>459400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>462800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>476200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>453200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>504900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>527200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>505900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>538200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>551900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4227700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4234200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3900800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5155900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5685000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5566500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5547100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5364300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5748000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5760300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5902900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6126600</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25591200</v>
+      </c>
+      <c r="E66" s="3">
         <v>26808300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26848700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25726900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22341700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21049500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22369800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24257200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22778300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23120100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24030100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22873600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24028400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24344900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25040600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>24502700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>24767300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25297900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26044400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25015300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>25235400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25494500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24785400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26262000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>28303700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26082600</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5220,11 +5388,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>439700</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -5232,31 +5400,34 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>430400</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>427500</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>420000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>405300</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>396000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>412000</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>433100</v>
       </c>
       <c r="AB70" s="3">
         <v>433100</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>433100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28481700</v>
+      </c>
+      <c r="E72" s="3">
         <v>28471200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28196500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28391400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27416300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24837900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23211500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24698900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22906900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22689600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22807600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21921000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21572100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20914800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>48985800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>29930000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>27626900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20115900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18075200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17829200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>16715300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15557000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14519200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15095200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14439300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14583300</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34470500</v>
+      </c>
+      <c r="E76" s="3">
         <v>34292300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33570500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>33950500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>33186100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>32234100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30970100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>31589300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30589300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30203900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29490400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>29870900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>29149600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28410500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28277000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>30540600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>28241600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24867100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22702100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21764100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19992000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18904200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16506000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18195400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19057100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19375700</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,93 +6004,99 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5944,44 +6139,47 @@
       <c r="P81" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R81" s="3">
         <v>725500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>997500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>943400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>954800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>869400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>819500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>788200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>762500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>434900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>835500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>316400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>497500</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,77 +6208,78 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>509700</v>
+      </c>
+      <c r="E83" s="3">
         <v>303500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>117000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>500800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>478900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>489800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>399000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>460400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>481400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>495400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>392800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>450200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>462100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>477700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>662300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>507900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>578900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>466600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>514900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>478100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>443300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>432800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,77 +6704,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>691200</v>
+      </c>
+      <c r="E89" s="3">
         <v>943200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1515800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1781100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>665900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>600700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1274500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1626100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>922500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1116600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1163900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1328300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>679000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>926800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1124200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1677200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>927100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>911400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1132900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1579800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>939500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1241300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,77 +6820,78 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-293600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-522700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-493100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-443500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-352300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-525900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-422400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-508600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-338600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-564200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-564800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-453000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-323100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-621500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-532000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-477000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-299000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-498000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-266000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-517000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-268700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-321600</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,77 +7067,80 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-694600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-870900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-684500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3656000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-167900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-453000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-655300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1893800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-32100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-743300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-498500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-370400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>152800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1337500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-272500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-672200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-855200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1181600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-381600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-688100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-255000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-353200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,62 +7183,63 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1169900</v>
+      </c>
+      <c r="E96" s="3">
         <v>15700</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3">
         <v>1166200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>49700</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="3">
         <v>1047900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>56100</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P96" s="3">
         <v>1159400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>97800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-260100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -7013,11 +7247,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-191500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,77 +7513,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-899100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-71300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-246600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3172600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-301800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1739300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1290000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>810800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-385700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-115400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1076600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-319600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-633200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>134700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-551600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-982400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>181700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-341800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-346900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1216900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1121500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7350,77 +7596,80 @@
       <c r="AB100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-43000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-23500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>7300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-24400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7430,77 +7679,80 @@
       <c r="AB101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>573000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1273000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>189100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1634600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-667800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>529800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>499300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>255700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-424500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>640300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>193200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-293400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>275800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>27000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>261100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-607600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>406500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-324100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-438000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>901400</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>16</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
